--- a/Шаблон ЦА-Проблема-Решение.xlsx
+++ b/Шаблон ЦА-Проблема-Решение.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\YandexDisk\Обучение\Вайб_кодинг\FS_PC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{888C1862-FD02-466A-8162-A36ED3C59C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FCA7C946-4746-4644-92A3-0D7CD9B9E59A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{63A5A80A-E38E-4095-B835-B9595B621913}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{63A5A80A-E38E-4095-B835-B9595B621913}"/>
   </bookViews>
   <sheets>
     <sheet name="НИПИ, ИТ, КБ" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,7 @@
     <sheet name="Кап.строй" sheetId="2" r:id="rId4"/>
     <sheet name="Девелопмент" sheetId="5" r:id="rId5"/>
     <sheet name="Фарма" sheetId="6" r:id="rId6"/>
-    <sheet name="архив" sheetId="8" r:id="rId7"/>
-    <sheet name="Иное" sheetId="9" r:id="rId8"/>
+    <sheet name="Иное" sheetId="9" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="57">
   <si>
     <t>Гипотеза</t>
   </si>
@@ -85,9 +84,6 @@
     <t>Данные по проектам разрозненны; Невозможно оценить состояние проектов в моменте</t>
   </si>
   <si>
-    <t>(пока нет данных)</t>
-  </si>
-  <si>
     <t>Кейс</t>
   </si>
   <si>
@@ -95,9 +91,6 @@
   </si>
   <si>
     <t>БЗ Производство тр</t>
-  </si>
-  <si>
-    <t>Проекты-Закупки-Производство (инжиниринг)</t>
   </si>
   <si>
     <t>Нереалистичные сроки еще на стадии планирования обусловлены разрывом между проектом, закупками и производством</t>
@@ -110,9 +103,6 @@
   </si>
   <si>
     <t>Невозможно управлять портфелем проектов как единой системой и видеть актуальные сроки проектов и бюджеты организации</t>
-  </si>
-  <si>
-    <t>Длинноцикловое производство</t>
   </si>
   <si>
     <t>Кап.Строй</t>
@@ -130,216 +120,10 @@
     <t>Необходимость отказа от управления проектами кап.строя в Excel</t>
   </si>
   <si>
-    <t>ЦА</t>
-  </si>
-  <si>
-    <t>Решение</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - РП каждого проекта и ответственный по каждой задаче 
- - внутри проекта КСГ проекта /актируемые этапы –план/факт сроков с  ответственными</t>
-  </si>
-  <si>
-    <t>Ценность</t>
-  </si>
-  <si>
-    <t>Руководитель видит, кто ответственный за каждый проект и каждую задачу</t>
-  </si>
-  <si>
-    <t>Единая панель по портфелю проектов с индикаторами состояния проекта по срокам, бюджету и наличия рисков</t>
-  </si>
-  <si>
-    <t>Руководитель сразу видит проблемные проектыи может оперативно реагировать
-Управляем портфелем как системой</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Единый ЖЦ проектов
-- Единая структура этапов и КТ
-- Единый формат дорожной карты проектов
-- Единая шкала статусов готовности и % исполнения задач</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Проекты становятся сопоставимыми между собой 
-Управление через решения и контрольные точки, а не через бесконечные совещания </t>
-  </si>
-  <si>
     <t>Экономика и сроки ведутся в разных инструментах. Не видны изменения бюджетов проектов при изменении сроков. Отчетность по портфелю собирается вручную из разрозненных файлов. Подготовленный отчет уже не актуален</t>
   </si>
   <si>
-    <t xml:space="preserve"> - Сквозное решение для управления сроками и бюджетами проектов
-- Пользователь один раз задает сроки актирования и условия оплаты по проекту, а система сама рассчитывает сроки поступлений и платежей
-- Актуализация данных в системе по мере возникновения информации, а не под отчет</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - При расчете календарного плана проекта БДР и БДДС проекта по периодам рассчитываются автоматически
-- Руководитель видит не только статус сроков проектов, но и их финансовые последствия
-- Отчет по актуальным данным доступен в любой момент времени проблемы выявляются раньше, чем они превращаются в срыв сроков или неисполнение бюджета</t>
-  </si>
-  <si>
     <t>Факт по бюджетам ведется в учетной системе и не сопоставим с планом. Нужно видеть факт в проектах вплоть до первичных документов. Двойной ввод данных</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Ввод факта напрямую в системе или интеграции с учётными системами (опционально)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Единый источник правды
-- Факт по проектам можно проверить вплоть до первички
-- РП не тратит время на ручное сопоставление план/факт</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Автоматическая актуализация прогноза по факту (опционально)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Всегда актуальный прогноз, не зависящий от человеческого фактора</t>
-  </si>
-  <si>
-    <t>Для компаний с начальным уровнем проектного управления (внешние проекты - оборот 800М до 4Я), (внутренние проекты - оборот от 2Я).
-Генеральный директор / РПО / ТОП Менеджер (ответсвенный за проектную деятельность) - потребитель отчетности от РП.
-Осуществляет контроль за ходом реализации реестра проектов в одном окне (Вехи), показатели (план/факт сроки, бюджеты, риски). В основном контроль за внутренними проектами.</t>
-  </si>
-  <si>
-    <t>Компании: 
-Осуществляют проектную деятельность, в портфеле 10+ проектов, с высокой долей расходов на трудовые ресурсы
-Отрасли: НИПИ, Трудоёмкое производство (КБ, ИТ, Консалтинг, Медиа, НИОКР без производства)
-Сегмент: 800млн - 4 млрд
-ЛПР: Директор по производству, Дирктор проектного офиса, Гл. инженер - тот, кто управляет сроками и объемами работ и загрузкой
-Исполнитель: ИТ</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Единый подход к планированию проектов
--  Оптимизировать процесс планирования с помощью шаблонирования и типизации
-- Рабочее место руководителей подразделений и взаимодействие с РП  в единой системе
-- Мониторинг состояния проектов через панель показателей
-- Количественный и качественный анализ переделок по проектам, выявление и устранение наиболее горящих причин переделок</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Дашборд, на котором смотрим, выполним ли план, когда нужны доп.ресурсы, а когда доп.проекты
-- Балансировка загрузки
-- Своевременное привлечение для выполнения работ более оптимального субподряда
-- Актуальные планы проектов в режиме реального времени
-- Мониторинг состояния портфеля проектов: все проекты в единой системе, мониторинг состояния проектов через панель показателей, план-факт</t>
-  </si>
-  <si>
-    <t>Прогнозирование и мониторинг Объемов работ и загрузки подразделений:
--  Дашборд, на котором смотрим, выполним ли план, когда нужны доп.ресурсы, а когда доп.проекты
-- Балансировка загрузки
-- Своевременное привлечение для выполнения работ более оптимального субподряда</t>
-  </si>
-  <si>
-    <t>Мониторинг потерь времени:
-- Количественный и качественный анализ переделок по проектам, выявление и устранение наиболее горящих причин переделок
-- Выявление непроизводительных трудозатрат и их «владельца» 
-- Контроль лимитов по видам проектных и непроектных трудозатрат</t>
-  </si>
-  <si>
-    <t>Рабочее место руководителей подразделений и взаимодействие с РП  в единой системе</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Единый подход к планированию проектов
-- Оптимизировать процесс планирования с помощью шаблонирования и типизации
--  «Типовой шаблон» для каждого стандартизируемого вида работ, на примере эффективно выполненного проекта
-- Контроль процента стандартизированных работ в портфеле</t>
-  </si>
-  <si>
-    <t>(см. отдельным листом)</t>
-  </si>
-  <si>
-    <t>ГД, Финансовый директор</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Выполняем проекты в срок
-- Выстраеваем систему контроля</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Повышение маржинальности по проектам за счет уменьшения переделок
-- Эффективное управление подразделением за счет сокращения непроектных (непроизводительных) трудозатрат</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Равномерная загрузка проектного производства
-- Контроль выполнения объемов работ </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Выстроена система контроля
-- Порядок на производстве</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Верхнеуровневое планирование - возможность планировать и управлять без ухода в конкретные детали проекта 
-- Готовые рабочие места для директора проектного производства (управление объемами и загрузкой), руководителя проектного подразделения (управление загрузкой сотрудников) и руководителя проекта (управление сроками и стоимостью проекта)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Объединяем и актуализируем все планы по проектам в единой системе
-- Мониторинг состояния проектов через панель показателей
-- Контроль план-факта выполнения объемов </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Сквозной процесс ГИП-Руководитель подразделения-Исполнитель (как сверху вниз, так и сверху вниз),  т.е. прозрачность планирования и факта исполнения человекочасов
-- Удобное годовое планирование</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Повышение маржинальности  по проектам за счет уменьшения переделок
-- Эффективное управление подразделением за счет сокращения непроектных (непроизводительных) трудозатрат</t>
-  </si>
-  <si>
-    <t>Финансовый директор (см. отдельным листом)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Отрасли: 
-Инжиниринг:
-- Компании, реализующие EPC контракты связанные с поставкой и пусконаладкой оборудования (НЕ строительство зданий, сооружений, дорог)
-- Делают комплексный проект
-- В начале есть обследование и проектирование (конструирование)
-- А внутри, когда они создают решение - это и есть позаказное производство. Просто позаказное пр-во не нуждается в нас т.к. им достаточно ERP. А когда есть работы до и работы после и их нужно связать в сложный проект и таких проектов много, им нужны мы, чтобы все связать
- - EPC проектирование, см. Пусконаладка,
-Размер компаний:
-800 млн. - 10 млрд 
-Заказчики-люди:  
-№1 - Владелец контрактов (портфеля заказов) - это КД, Гл инженер или ФД, он отвечает перед заказчиками и зависит от смежных структур
-</t>
-  </si>
-  <si>
-    <t>Исполнимый план, в котором увязаны сроки проектирования, закупок, поставок, производства и пусконаладки</t>
-  </si>
-  <si>
-    <t>Сквозной процесс «Проекты-Закупки-Производство-ПНР и управление с 2-х точек зрения – проектов и портфеля</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Обеспечение прозрачности цикла: Проект-Закупка-Производство-Проект
-- Формирование плана закупки и производства на основании потребностей проектов
-- Синхронизация плановых сроков проекта со сроками закупки номенклатуры
-- Синхронизация плановых сроков проекта со сроками выпуска готовой продукции</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Автоактуализация сроков проектов по данным закупок и производства с отображением в графике каждого проекта, графиках смежных подразделений и в сводных графиках по портфелю
-- Выстроенный процесс обмена информацией при замене спецификации оборудования
-- Актуальный прогноз загрузки бригад на проектах
-- Актуальный прогноз сроков отгрузки/поставки заказчику</t>
-  </si>
-  <si>
-    <t>Сводная картина проекта всегда актуальна: графики и экономика подразделений обновляются автоматически.
-Мы видим критичные изменения в проекте и их влияние на сроки.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Автоматическая актуализация экономики проектов по изменениям из 1С:ERP
-- Сравнение договорного и прогнозного планов по маржинальности и денежному потоку
-- План-фактный анализ результатов, ресурсов БДР, БДДС
-- Реализация товаров и услуг
-- Оценка стоимости денег
-- Панель KPI: Контроль рентабельности</t>
-  </si>
-  <si>
-    <t>Вся актуальная информация об экономике проекта доступна в режиме единого окна</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Аналитические отчеты не только по отдельным проектам, но и по сводному портфелю и его состоянию
-- P&amp;L и Cash Flow по портфелю в реальном времени по нескольким сценариям
-- Унифицированный подход к формированию структуры работ проектов. Использование шаблонов
-- Использование единого набора показателей для контроля исполнения проектов
-- Учет не только текущих, но и перспективных проектов</t>
-  </si>
-  <si>
-    <t>Сегмент - Ultra 10млрд+, все отрасли
-- Директор по инвестициям
-- или может быть бюджетом конкретного проекта - директор этого проекта</t>
   </si>
   <si>
     <t>Уровень зрелости</t>
@@ -494,7 +278,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -555,21 +339,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -586,39 +355,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -664,16 +402,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -714,33 +464,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -975,51 +698,7 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp59.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp60.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp61.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp62.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp63.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp64.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp65.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp66.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp67.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp68.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp69.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -1027,71 +706,7 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp70.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp71.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp72.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp73.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp74.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp75.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp76.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp77.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp78.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp79.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
 <file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp80.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp81.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp82.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp83.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp84.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp85.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -4959,1820 +4574,6 @@
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00000A100000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>5</xdr:col>
-          <xdr:colOff>247650</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>400050</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5129" name="Check Box 9" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5129"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000009140000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>371475</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>400050</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5149" name="Check Box 29" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5149"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00001D140000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>371475</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>400050</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5150" name="Check Box 30" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5150"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00001E140000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>371475</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>400050</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5151" name="Check Box 31" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5151"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00001F140000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>371475</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>400050</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5152" name="Check Box 32" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5152"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000020140000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>371475</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>400050</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5153" name="Check Box 33" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5153"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000021140000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>8</xdr:row>
-          <xdr:rowOff>66675</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>381000</xdr:colOff>
-          <xdr:row>8</xdr:row>
-          <xdr:rowOff>285750</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5154" name="Check Box 34" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5154"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000022140000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>9</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>371475</xdr:colOff>
-          <xdr:row>9</xdr:row>
-          <xdr:rowOff>400050</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5155" name="Check Box 35" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5155"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000023140000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>10</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>371475</xdr:colOff>
-          <xdr:row>10</xdr:row>
-          <xdr:rowOff>400050</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5156" name="Check Box 36" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5156"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000024140000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>371475</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>400050</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5157" name="Check Box 37" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5157"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000025140000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>371475</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>400050</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5158" name="Check Box 38" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5158"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000026140000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>371475</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>400050</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5159" name="Check Box 39" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5159"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000027140000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>14</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>371475</xdr:colOff>
-          <xdr:row>14</xdr:row>
-          <xdr:rowOff>400050</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5160" name="Check Box 40" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5160"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000028140000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>15</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>371475</xdr:colOff>
-          <xdr:row>15</xdr:row>
-          <xdr:rowOff>400050</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5161" name="Check Box 41" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5161"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000029140000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>16</xdr:row>
-          <xdr:rowOff>152400</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>381000</xdr:colOff>
-          <xdr:row>18</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5162" name="Check Box 42" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5162"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00002A140000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>18</xdr:row>
-          <xdr:rowOff>685800</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>381000</xdr:colOff>
-          <xdr:row>18</xdr:row>
-          <xdr:rowOff>895350</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5163" name="Check Box 43" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5163"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00002B140000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>19</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>371475</xdr:colOff>
-          <xdr:row>19</xdr:row>
-          <xdr:rowOff>400050</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5164" name="Check Box 44" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5164"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00002C140000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>20</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>371475</xdr:colOff>
-          <xdr:row>20</xdr:row>
-          <xdr:rowOff>400050</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5165" name="Check Box 45" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5165"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00002D140000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>21</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>371475</xdr:colOff>
-          <xdr:row>21</xdr:row>
-          <xdr:rowOff>400050</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5166" name="Check Box 46" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5166"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00002E140000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>22</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>371475</xdr:colOff>
-          <xdr:row>22</xdr:row>
-          <xdr:rowOff>400050</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5167" name="Check Box 47" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5167"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00002F140000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>23</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>371475</xdr:colOff>
-          <xdr:row>23</xdr:row>
-          <xdr:rowOff>400050</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5168" name="Check Box 48" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5168"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000030140000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>24</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>371475</xdr:colOff>
-          <xdr:row>24</xdr:row>
-          <xdr:rowOff>400050</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5169" name="Check Box 49" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5169"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000031140000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>25</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>371475</xdr:colOff>
-          <xdr:row>25</xdr:row>
-          <xdr:rowOff>400050</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5170" name="Check Box 50" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5170"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000032140000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>26</xdr:row>
-          <xdr:rowOff>180975</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>371475</xdr:colOff>
-          <xdr:row>27</xdr:row>
-          <xdr:rowOff>209550</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5171" name="Check Box 51" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5171"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000033140000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>28</xdr:row>
-          <xdr:rowOff>104775</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>381000</xdr:colOff>
-          <xdr:row>28</xdr:row>
-          <xdr:rowOff>323850</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5172" name="Check Box 52" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5172"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000034140000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>28</xdr:row>
-          <xdr:rowOff>361950</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>381000</xdr:colOff>
-          <xdr:row>30</xdr:row>
-          <xdr:rowOff>19050</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5173" name="Check Box 53" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5173"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000035140000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>133350</xdr:colOff>
-          <xdr:row>25</xdr:row>
-          <xdr:rowOff>1619250</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>3</xdr:col>
-          <xdr:colOff>381000</xdr:colOff>
-          <xdr:row>27</xdr:row>
-          <xdr:rowOff>9525</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5174" name="Check Box 54" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s5174"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000036140000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7119,370 +4920,370 @@
   <dimension ref="A1:G32"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" style="15" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="20" customWidth="1"/>
-    <col min="3" max="3" width="51.42578125" style="25" customWidth="1"/>
-    <col min="4" max="4" width="5" style="21" customWidth="1"/>
-    <col min="5" max="5" width="83.28515625" style="21" customWidth="1"/>
-    <col min="6" max="6" width="23.7109375" style="21" customWidth="1"/>
-    <col min="7" max="7" width="33.85546875" style="15" customWidth="1"/>
-    <col min="8" max="16384" width="8.85546875" style="15"/>
+    <col min="1" max="1" width="4.5703125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="9" customWidth="1"/>
+    <col min="3" max="3" width="51.42578125" style="14" customWidth="1"/>
+    <col min="4" max="4" width="5" style="10" customWidth="1"/>
+    <col min="5" max="5" width="83.28515625" style="10" customWidth="1"/>
+    <col min="6" max="6" width="23.7109375" style="10" customWidth="1"/>
+    <col min="7" max="7" width="33.85546875" style="4" customWidth="1"/>
+    <col min="8" max="16384" width="8.85546875" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="G1" s="15" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="22"/>
-      <c r="B3" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23" t="s">
+      <c r="B1" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="11"/>
+      <c r="B3" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="G3" s="22" t="s">
+      <c r="F3" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="11" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="31"/>
-      <c r="B4" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" s="35" t="s">
-        <v>78</v>
-      </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="27" t="s">
+      <c r="A4" s="24"/>
+      <c r="B4" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="13"/>
-      <c r="G4" s="38" t="s">
+      <c r="F4" s="2"/>
+      <c r="G4" s="31" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="31"/>
-      <c r="B5" s="33"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="27" t="s">
+      <c r="A5" s="24"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="13"/>
-      <c r="G5" s="38"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="31"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="31"/>
-      <c r="B6" s="33"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="27" t="s">
+      <c r="A6" s="24"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="13"/>
-      <c r="G6" s="38"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="31"/>
     </row>
     <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="31"/>
-      <c r="B7" s="33"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="38"/>
+      <c r="A7" s="24"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="31"/>
     </row>
     <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="31"/>
-      <c r="B8" s="33"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" s="13"/>
-      <c r="G8" s="38"/>
+      <c r="A8" s="24"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="31"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="33"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="27" t="s">
+      <c r="A9" s="24"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="13"/>
-      <c r="G9" s="38"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="31"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="31"/>
-      <c r="B10" s="33"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="38"/>
+      <c r="A10" s="24"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="31"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="38"/>
+      <c r="A11" s="24"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="31"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="31"/>
-      <c r="B12" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" s="35" t="s">
-        <v>79</v>
-      </c>
-      <c r="D12" s="13"/>
-      <c r="E12" s="27" t="s">
+      <c r="A12" s="24"/>
+      <c r="B12" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="13"/>
-      <c r="G12" s="38" t="s">
-        <v>17</v>
+      <c r="F12" s="2"/>
+      <c r="G12" s="31" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="31"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="27" t="s">
+      <c r="A13" s="24"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="13"/>
-      <c r="G13" s="38"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="31"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="31"/>
-      <c r="B14" s="33"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="27" t="s">
+      <c r="A14" s="24"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="13"/>
-      <c r="G14" s="38"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="31"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="31"/>
-      <c r="B15" s="33"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="27" t="s">
+      <c r="A15" s="24"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="13"/>
-      <c r="G15" s="38"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="31"/>
     </row>
     <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="31"/>
-      <c r="B16" s="33"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="27" t="s">
+      <c r="A16" s="24"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F16" s="13"/>
-      <c r="G16" s="38"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="31"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="31"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="27" t="s">
+      <c r="A17" s="24"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="13"/>
-      <c r="G17" s="38"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="31"/>
     </row>
     <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="31"/>
-      <c r="B18" s="33"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="27" t="s">
+      <c r="A18" s="24"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="F18" s="13"/>
-      <c r="G18" s="38"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="31"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="31"/>
-      <c r="B19" s="33"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="38"/>
+      <c r="A19" s="24"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="31"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="31"/>
-      <c r="B20" s="34"/>
-      <c r="C20" s="37"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="38"/>
+      <c r="A20" s="24"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="31"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="39"/>
-      <c r="B21" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" s="35" t="s">
-        <v>80</v>
-      </c>
-      <c r="D21" s="13"/>
-      <c r="E21" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="F21" s="13"/>
-      <c r="G21" s="32" t="s">
-        <v>16</v>
+      <c r="A21" s="32"/>
+      <c r="B21" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" s="2"/>
+      <c r="G21" s="25" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="40"/>
-      <c r="B22" s="33"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="F22" s="13"/>
-      <c r="G22" s="33"/>
+      <c r="A22" s="33"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F22" s="2"/>
+      <c r="G22" s="26"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="40"/>
-      <c r="B23" s="33"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="27" t="s">
-        <v>99</v>
-      </c>
-      <c r="F23" s="13"/>
-      <c r="G23" s="33"/>
+      <c r="A23" s="33"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F23" s="2"/>
+      <c r="G23" s="26"/>
     </row>
     <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="40"/>
-      <c r="B24" s="33"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="F24" s="13"/>
-      <c r="G24" s="33"/>
+      <c r="A24" s="33"/>
+      <c r="B24" s="26"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F24" s="2"/>
+      <c r="G24" s="26"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="40"/>
-      <c r="B25" s="33"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="F25" s="13"/>
-      <c r="G25" s="33"/>
+      <c r="A25" s="33"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="F25" s="2"/>
+      <c r="G25" s="26"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="40"/>
-      <c r="B26" s="33"/>
-      <c r="C26" s="36"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="F26" s="13"/>
-      <c r="G26" s="33"/>
+      <c r="A26" s="33"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="F26" s="2"/>
+      <c r="G26" s="26"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="40"/>
-      <c r="B27" s="33"/>
-      <c r="C27" s="36"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="F27" s="13"/>
-      <c r="G27" s="33"/>
+      <c r="A27" s="33"/>
+      <c r="B27" s="26"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F27" s="2"/>
+      <c r="G27" s="26"/>
     </row>
     <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="40"/>
-      <c r="B28" s="33"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="F28" s="13"/>
-      <c r="G28" s="33"/>
+      <c r="A28" s="33"/>
+      <c r="B28" s="26"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="F28" s="2"/>
+      <c r="G28" s="26"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="40"/>
-      <c r="B29" s="33"/>
-      <c r="C29" s="36"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="F29" s="13"/>
-      <c r="G29" s="33"/>
+      <c r="A29" s="33"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="F29" s="2"/>
+      <c r="G29" s="26"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="40"/>
-      <c r="B30" s="33"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="33"/>
+      <c r="A30" s="33"/>
+      <c r="B30" s="26"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="26"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="41"/>
-      <c r="B31" s="34"/>
-      <c r="C31" s="37"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="34"/>
+      <c r="A31" s="34"/>
+      <c r="B31" s="27"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="27"/>
     </row>
     <row r="32" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="18"/>
-      <c r="B32" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="C32" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="D32" s="13"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="18" t="s">
-        <v>15</v>
+      <c r="A32" s="7"/>
+      <c r="B32" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D32" s="2"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -8156,276 +5957,276 @@
   <dimension ref="A1:H23"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4" style="15" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="20" customWidth="1"/>
-    <col min="3" max="3" width="37" style="25" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" style="21" customWidth="1"/>
-    <col min="5" max="5" width="67.42578125" style="21" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" style="21" customWidth="1"/>
-    <col min="7" max="7" width="33.85546875" style="15" customWidth="1"/>
-    <col min="8" max="16384" width="8.85546875" style="15"/>
+    <col min="1" max="1" width="4" style="4" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="9" customWidth="1"/>
+    <col min="3" max="3" width="37" style="14" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" style="10" customWidth="1"/>
+    <col min="5" max="5" width="67.42578125" style="10" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" style="10" customWidth="1"/>
+    <col min="7" max="7" width="33.85546875" style="4" customWidth="1"/>
+    <col min="8" max="16384" width="8.85546875" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="42" t="s">
-        <v>86</v>
-      </c>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="15" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" s="12" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="22"/>
-      <c r="B3" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23" t="s">
+      <c r="B1" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="11"/>
+      <c r="B3" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="G3" s="22" t="s">
+      <c r="F3" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="11" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="31"/>
-      <c r="B4" s="38" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" s="43" t="s">
-        <v>82</v>
-      </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13" t="s">
+      <c r="A4" s="24"/>
+      <c r="B4" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="36" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="24"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="36"/>
+    </row>
+    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="24"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="13"/>
-      <c r="G4" s="43" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="31"/>
-      <c r="B5" s="38"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13" t="s">
+      <c r="F6" s="2"/>
+      <c r="G6" s="36"/>
+    </row>
+    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="24"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="13"/>
-      <c r="G5" s="43"/>
-    </row>
-    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="31"/>
-      <c r="B6" s="38"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="13"/>
-      <c r="G6" s="43"/>
-    </row>
-    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="31"/>
-      <c r="B7" s="38"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="43"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="36"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="31"/>
-      <c r="B8" s="38"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="43"/>
+      <c r="A8" s="24"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="36"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="43"/>
+      <c r="A9" s="24"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="36"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="39"/>
-      <c r="B10" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" s="35" t="s">
-        <v>80</v>
-      </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="F10" s="13"/>
-      <c r="G10" s="32" t="s">
-        <v>16</v>
+      <c r="A10" s="32"/>
+      <c r="B10" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="25" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="40"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="F11" s="13"/>
-      <c r="G11" s="33"/>
+      <c r="A11" s="33"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="26"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="40"/>
-      <c r="B12" s="33"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="F12" s="13"/>
-      <c r="G12" s="33"/>
+      <c r="A12" s="33"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="26"/>
     </row>
     <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="40"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="F13" s="13"/>
-      <c r="G13" s="33"/>
+      <c r="A13" s="33"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="26"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="40"/>
-      <c r="B14" s="33"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="F14" s="13"/>
-      <c r="G14" s="33"/>
+      <c r="A14" s="33"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="26"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="40"/>
-      <c r="B15" s="33"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="F15" s="13"/>
-      <c r="G15" s="33"/>
+      <c r="A15" s="33"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="26"/>
     </row>
     <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="40"/>
-      <c r="B16" s="33"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="F16" s="13"/>
-      <c r="G16" s="33"/>
+      <c r="A16" s="33"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="26"/>
     </row>
     <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="40"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="F17" s="13"/>
-      <c r="G17" s="33"/>
+      <c r="A17" s="33"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="26"/>
     </row>
     <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="40"/>
-      <c r="B18" s="33"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="F18" s="13"/>
-      <c r="G18" s="33"/>
+      <c r="A18" s="33"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="26"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="40"/>
-      <c r="B19" s="33"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="33"/>
+      <c r="A19" s="33"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="26"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="41"/>
-      <c r="B20" s="34"/>
-      <c r="C20" s="37"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="34"/>
+      <c r="A20" s="34"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="27"/>
     </row>
     <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="18"/>
-      <c r="B21" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" s="19"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="26" t="s">
-        <v>87</v>
+      <c r="A21" s="7"/>
+      <c r="B21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="8"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="15" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="18"/>
-      <c r="B22" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" s="19"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="26" t="s">
-        <v>88</v>
+      <c r="A22" s="7"/>
+      <c r="B22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="8"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="15" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="90" x14ac:dyDescent="0.25">
-      <c r="A23" s="18"/>
-      <c r="B23" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="C23" s="19"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="26" t="s">
-        <v>89</v>
+      <c r="A23" s="7"/>
+      <c r="B23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="8"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="15" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -8831,132 +6632,132 @@
   <dimension ref="A1:G11"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4" style="15" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="20" customWidth="1"/>
-    <col min="3" max="3" width="51.42578125" style="25" customWidth="1"/>
-    <col min="4" max="4" width="3.85546875" style="21" customWidth="1"/>
-    <col min="5" max="5" width="83.28515625" style="21" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" style="21" customWidth="1"/>
-    <col min="7" max="7" width="33.85546875" style="15" customWidth="1"/>
-    <col min="8" max="16384" width="8.85546875" style="15"/>
+    <col min="1" max="1" width="4" style="4" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="9" customWidth="1"/>
+    <col min="3" max="3" width="51.42578125" style="14" customWidth="1"/>
+    <col min="4" max="4" width="3.85546875" style="10" customWidth="1"/>
+    <col min="5" max="5" width="83.28515625" style="10" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" style="10" customWidth="1"/>
+    <col min="7" max="7" width="33.85546875" style="4" customWidth="1"/>
+    <col min="8" max="16384" width="8.85546875" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="G1" s="15" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="22"/>
-      <c r="B3" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23" t="s">
+      <c r="B1" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="11"/>
+      <c r="B3" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="G3" s="22" t="s">
+      <c r="F3" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="11" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="31"/>
-      <c r="B4" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" s="35" t="s">
-        <v>78</v>
-      </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13" t="s">
+      <c r="A4" s="24"/>
+      <c r="B4" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="13"/>
-      <c r="G4" s="38" t="s">
+      <c r="F4" s="19"/>
+      <c r="G4" s="31" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="31"/>
-      <c r="B5" s="33"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13" t="s">
+      <c r="A5" s="24"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="13"/>
-      <c r="G5" s="38"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="31"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="31"/>
-      <c r="B6" s="33"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13" t="s">
+      <c r="A6" s="24"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="13"/>
-      <c r="G6" s="38"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="31"/>
     </row>
     <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="31"/>
-      <c r="B7" s="33"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="38"/>
+      <c r="A7" s="24"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="19"/>
+      <c r="G7" s="31"/>
     </row>
     <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="31"/>
-      <c r="B8" s="33"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" s="13"/>
-      <c r="G8" s="38"/>
+      <c r="A8" s="24"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="19"/>
+      <c r="G8" s="31"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="33"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13" t="s">
+      <c r="A9" s="24"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="13"/>
-      <c r="G9" s="38"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="31"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="31"/>
-      <c r="B10" s="33"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="38"/>
+      <c r="A10" s="24"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="31"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="38"/>
+      <c r="A11" s="24"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -9158,110 +6959,110 @@
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4" style="15" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="20" customWidth="1"/>
-    <col min="3" max="3" width="37" style="25" customWidth="1"/>
-    <col min="4" max="4" width="5.42578125" style="21" customWidth="1"/>
-    <col min="5" max="5" width="67.42578125" style="21" customWidth="1"/>
-    <col min="6" max="6" width="19.7109375" style="21" customWidth="1"/>
-    <col min="7" max="7" width="33.85546875" style="15" customWidth="1"/>
-    <col min="8" max="16384" width="8.85546875" style="15"/>
+    <col min="1" max="1" width="4" style="4" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="9" customWidth="1"/>
+    <col min="3" max="3" width="37" style="14" customWidth="1"/>
+    <col min="4" max="4" width="5.42578125" style="10" customWidth="1"/>
+    <col min="5" max="5" width="67.42578125" style="10" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" style="10" customWidth="1"/>
+    <col min="7" max="7" width="33.85546875" style="4" customWidth="1"/>
+    <col min="8" max="16384" width="8.85546875" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="G1" s="15" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="22"/>
-      <c r="B3" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23" t="s">
+      <c r="B1" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="11"/>
+      <c r="B3" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="G3" s="22" t="s">
+      <c r="F3" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="11" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="31"/>
-      <c r="B4" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="C4" s="35" t="s">
-        <v>83</v>
-      </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13" t="s">
+      <c r="A4" s="24"/>
+      <c r="B4" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="19"/>
+      <c r="G4" s="31" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="24"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="19"/>
+      <c r="G5" s="31"/>
+    </row>
+    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="24"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="19"/>
+      <c r="G6" s="31"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="24"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="13"/>
-      <c r="G4" s="38" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="31"/>
-      <c r="B5" s="33"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="13"/>
-      <c r="G5" s="38"/>
-    </row>
-    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="31"/>
-      <c r="B6" s="33"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="13"/>
-      <c r="G6" s="38"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="31"/>
-      <c r="B7" s="33"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="38"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="31"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="31"/>
-      <c r="B8" s="33"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="38"/>
+      <c r="A8" s="24"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="31"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="34"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="38"/>
+      <c r="A9" s="24"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -9375,173 +7176,173 @@
   <dimension ref="A1:F20"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4" style="15" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="20" customWidth="1"/>
-    <col min="3" max="3" width="37" style="25" customWidth="1"/>
-    <col min="4" max="4" width="67.42578125" style="21" customWidth="1"/>
-    <col min="5" max="5" width="27" style="21" customWidth="1"/>
-    <col min="6" max="6" width="33.85546875" style="15" customWidth="1"/>
-    <col min="7" max="16384" width="8.85546875" style="15"/>
+    <col min="1" max="1" width="4" style="4" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="9" customWidth="1"/>
+    <col min="3" max="3" width="37" style="14" customWidth="1"/>
+    <col min="4" max="4" width="67.42578125" style="10" customWidth="1"/>
+    <col min="5" max="5" width="27" style="10" customWidth="1"/>
+    <col min="6" max="6" width="33.85546875" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="8.85546875" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F1" s="15" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="22"/>
-      <c r="B3" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="D3" s="23" t="s">
+      <c r="F1" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="11"/>
+      <c r="B3" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="F3" s="22" t="s">
+      <c r="E3" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="11" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="7"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="18"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="7"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="18"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="18"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="18"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="18"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="18"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="7"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="18"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="18"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="7"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="18"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="18"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="7"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="18"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="18"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="18"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="18"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="7"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="18"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="18"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="7"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="18"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="18"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="7"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="18"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="18"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="7"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="18"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="18"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="7"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="18"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="18"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="7"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="18"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="18"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="7"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="18"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="18"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="7"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="18"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="18"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9553,173 +7354,173 @@
   <dimension ref="A1:F20"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4" style="15" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="20" customWidth="1"/>
-    <col min="3" max="3" width="37" style="25" customWidth="1"/>
-    <col min="4" max="4" width="67.42578125" style="21" customWidth="1"/>
-    <col min="5" max="5" width="24.42578125" style="21" customWidth="1"/>
-    <col min="6" max="6" width="33.85546875" style="15" customWidth="1"/>
-    <col min="7" max="16384" width="8.85546875" style="15"/>
+    <col min="1" max="1" width="4" style="4" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="9" customWidth="1"/>
+    <col min="3" max="3" width="37" style="14" customWidth="1"/>
+    <col min="4" max="4" width="67.42578125" style="10" customWidth="1"/>
+    <col min="5" max="5" width="24.42578125" style="10" customWidth="1"/>
+    <col min="6" max="6" width="33.85546875" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="8.85546875" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F1" s="15" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="22"/>
-      <c r="B3" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="D3" s="23" t="s">
+      <c r="F1" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="11"/>
+      <c r="B3" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="F3" s="22" t="s">
+      <c r="E3" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="11" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="7"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="18"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="7"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="18"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="18"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="18"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="18"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="18"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="7"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="18"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="18"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="7"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="18"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="18"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="7"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="18"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="18"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="18"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="18"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="7"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="18"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="18"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="7"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="18"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="18"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="7"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="18"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="18"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="7"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="18"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="18"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="7"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="18"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="18"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="7"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="18"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="18"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="7"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="18"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="18"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="7"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="18"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="18"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9727,1271 +7528,177 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2670DE9-D580-4ED9-A93A-3995284BA958}">
-  <dimension ref="A3:H30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="34.140625" customWidth="1"/>
-    <col min="3" max="3" width="48.140625" customWidth="1"/>
-    <col min="4" max="4" width="7.28515625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="67.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="60.42578125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="48.28515625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="33.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="44"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="45" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H4" s="48" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="44"/>
-      <c r="B5" s="51"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H5" s="48"/>
-    </row>
-    <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A6" s="44"/>
-      <c r="B6" s="51"/>
-      <c r="C6" s="46"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H6" s="48"/>
-    </row>
-    <row r="7" spans="1:8" ht="135" x14ac:dyDescent="0.25">
-      <c r="A7" s="44"/>
-      <c r="B7" s="51"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="H7" s="48"/>
-    </row>
-    <row r="8" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A8" s="44"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H8" s="48"/>
-    </row>
-    <row r="9" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="44"/>
-      <c r="B9" s="52"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H9" s="48"/>
-    </row>
-    <row r="10" spans="1:8" ht="135" x14ac:dyDescent="0.25">
-      <c r="A10" s="44"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="45" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="H10" s="48" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="135" x14ac:dyDescent="0.25">
-      <c r="A11" s="44"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="H11" s="48"/>
-    </row>
-    <row r="12" spans="1:8" ht="105" x14ac:dyDescent="0.25">
-      <c r="A12" s="44"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="46"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H12" s="48"/>
-    </row>
-    <row r="13" spans="1:8" ht="120" x14ac:dyDescent="0.25">
-      <c r="A13" s="44"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="46"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="H13" s="48"/>
-    </row>
-    <row r="14" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A14" s="44"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H14" s="48"/>
-    </row>
-    <row r="15" spans="1:8" ht="90" x14ac:dyDescent="0.25">
-      <c r="A15" s="44"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="H15" s="48"/>
-    </row>
-    <row r="16" spans="1:8" ht="135" x14ac:dyDescent="0.25">
-      <c r="A16" s="44"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="H16" s="48"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F17" s="11"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18" s="11"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="145.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="44"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="45" t="s">
-        <v>65</v>
-      </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="H19" s="49" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="222" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="44"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="H20" s="49"/>
-    </row>
-    <row r="21" spans="1:8" ht="132.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="44"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="46"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H21" s="49"/>
-    </row>
-    <row r="22" spans="1:8" ht="137.44999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="44"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="47"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="H22" s="49"/>
-    </row>
-    <row r="23" spans="1:8" ht="120" x14ac:dyDescent="0.25">
-      <c r="A23" s="44"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="50"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="H23" s="48" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="120" x14ac:dyDescent="0.25">
-      <c r="A24" s="44"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="51"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="H24" s="48"/>
-    </row>
-    <row r="25" spans="1:8" ht="120" x14ac:dyDescent="0.25">
-      <c r="A25" s="44"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="51"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H25" s="48"/>
-    </row>
-    <row r="26" spans="1:8" ht="135" x14ac:dyDescent="0.25">
-      <c r="A26" s="44"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="52"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="H26" s="48"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="44"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="45" t="s">
-        <v>74</v>
-      </c>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="48" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="44"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="46"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="48"/>
-    </row>
-    <row r="29" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="44"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="46"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="48"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="44"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="47"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="48"/>
-    </row>
-  </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="B4:B9"/>
-    <mergeCell ref="C4:C9"/>
-    <mergeCell ref="H4:H9"/>
-    <mergeCell ref="A10:A16"/>
-    <mergeCell ref="C10:C16"/>
-    <mergeCell ref="H10:H16"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="C27:C30"/>
-    <mergeCell ref="H27:H30"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="C19:C22"/>
-    <mergeCell ref="H19:H22"/>
-    <mergeCell ref="A23:A26"/>
-    <mergeCell ref="C23:C26"/>
-    <mergeCell ref="H23:H26"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x14">
-      <controls>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="5129" r:id="rId3" name="Check Box 9">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>11</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>5</xdr:col>
-                    <xdr:colOff>247650</xdr:colOff>
-                    <xdr:row>11</xdr:row>
-                    <xdr:rowOff>400050</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="5149" r:id="rId4" name="Check Box 29">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>3</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>371475</xdr:colOff>
-                    <xdr:row>3</xdr:row>
-                    <xdr:rowOff>400050</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="5150" r:id="rId5" name="Check Box 30">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>4</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>371475</xdr:colOff>
-                    <xdr:row>4</xdr:row>
-                    <xdr:rowOff>400050</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="5151" r:id="rId6" name="Check Box 31">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>5</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>371475</xdr:colOff>
-                    <xdr:row>5</xdr:row>
-                    <xdr:rowOff>400050</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="5152" r:id="rId7" name="Check Box 32">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>6</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>371475</xdr:colOff>
-                    <xdr:row>6</xdr:row>
-                    <xdr:rowOff>400050</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="5153" r:id="rId8" name="Check Box 33">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>7</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>371475</xdr:colOff>
-                    <xdr:row>7</xdr:row>
-                    <xdr:rowOff>400050</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="5154" r:id="rId9" name="Check Box 34">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>8</xdr:row>
-                    <xdr:rowOff>66675</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>381000</xdr:colOff>
-                    <xdr:row>8</xdr:row>
-                    <xdr:rowOff>285750</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="5155" r:id="rId10" name="Check Box 35">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>9</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>371475</xdr:colOff>
-                    <xdr:row>9</xdr:row>
-                    <xdr:rowOff>400050</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="5156" r:id="rId11" name="Check Box 36">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>10</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>371475</xdr:colOff>
-                    <xdr:row>10</xdr:row>
-                    <xdr:rowOff>400050</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="5157" r:id="rId12" name="Check Box 37">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>11</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>371475</xdr:colOff>
-                    <xdr:row>11</xdr:row>
-                    <xdr:rowOff>400050</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="5158" r:id="rId13" name="Check Box 38">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>12</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>371475</xdr:colOff>
-                    <xdr:row>12</xdr:row>
-                    <xdr:rowOff>400050</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="5159" r:id="rId14" name="Check Box 39">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>13</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>371475</xdr:colOff>
-                    <xdr:row>13</xdr:row>
-                    <xdr:rowOff>400050</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="5160" r:id="rId15" name="Check Box 40">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>14</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>371475</xdr:colOff>
-                    <xdr:row>14</xdr:row>
-                    <xdr:rowOff>400050</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="5161" r:id="rId16" name="Check Box 41">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>15</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>371475</xdr:colOff>
-                    <xdr:row>15</xdr:row>
-                    <xdr:rowOff>400050</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="5162" r:id="rId17" name="Check Box 42">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>16</xdr:row>
-                    <xdr:rowOff>152400</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>381000</xdr:colOff>
-                    <xdr:row>18</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="5163" r:id="rId18" name="Check Box 43">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>18</xdr:row>
-                    <xdr:rowOff>685800</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>381000</xdr:colOff>
-                    <xdr:row>18</xdr:row>
-                    <xdr:rowOff>895350</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="5164" r:id="rId19" name="Check Box 44">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>19</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>371475</xdr:colOff>
-                    <xdr:row>19</xdr:row>
-                    <xdr:rowOff>400050</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="5165" r:id="rId20" name="Check Box 45">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>20</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>371475</xdr:colOff>
-                    <xdr:row>20</xdr:row>
-                    <xdr:rowOff>400050</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="5166" r:id="rId21" name="Check Box 46">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>21</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>371475</xdr:colOff>
-                    <xdr:row>21</xdr:row>
-                    <xdr:rowOff>400050</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="5167" r:id="rId22" name="Check Box 47">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>22</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>371475</xdr:colOff>
-                    <xdr:row>22</xdr:row>
-                    <xdr:rowOff>400050</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="5168" r:id="rId23" name="Check Box 48">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>23</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>371475</xdr:colOff>
-                    <xdr:row>23</xdr:row>
-                    <xdr:rowOff>400050</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="5169" r:id="rId24" name="Check Box 49">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>24</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>371475</xdr:colOff>
-                    <xdr:row>24</xdr:row>
-                    <xdr:rowOff>400050</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="5170" r:id="rId25" name="Check Box 50">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>25</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>371475</xdr:colOff>
-                    <xdr:row>25</xdr:row>
-                    <xdr:rowOff>400050</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="5171" r:id="rId26" name="Check Box 51">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>26</xdr:row>
-                    <xdr:rowOff>180975</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>371475</xdr:colOff>
-                    <xdr:row>27</xdr:row>
-                    <xdr:rowOff>209550</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="5172" r:id="rId27" name="Check Box 52">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>28</xdr:row>
-                    <xdr:rowOff>104775</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>381000</xdr:colOff>
-                    <xdr:row>28</xdr:row>
-                    <xdr:rowOff>323850</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="5173" r:id="rId28" name="Check Box 53">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>28</xdr:row>
-                    <xdr:rowOff>361950</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>381000</xdr:colOff>
-                    <xdr:row>30</xdr:row>
-                    <xdr:rowOff>19050</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="5174" r:id="rId29" name="Check Box 54">
-              <controlPr defaultSize="0" autoFill="0" autoLine="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>133350</xdr:colOff>
-                    <xdr:row>25</xdr:row>
-                    <xdr:rowOff>1619250</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>3</xdr:col>
-                    <xdr:colOff>381000</xdr:colOff>
-                    <xdr:row>27</xdr:row>
-                    <xdr:rowOff>9525</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-      </controls>
-    </mc:Choice>
-  </mc:AlternateContent>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{676BC8D6-EE13-432B-AC71-7EBB3068332C}">
   <dimension ref="A1:F20"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4" style="15" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="20" customWidth="1"/>
-    <col min="3" max="3" width="37" style="25" customWidth="1"/>
-    <col min="4" max="4" width="67.42578125" style="21" customWidth="1"/>
-    <col min="5" max="5" width="23.5703125" style="21" customWidth="1"/>
-    <col min="6" max="6" width="33.85546875" style="15" customWidth="1"/>
-    <col min="7" max="16384" width="8.85546875" style="15"/>
+    <col min="1" max="1" width="4" style="4" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="9" customWidth="1"/>
+    <col min="3" max="3" width="37" style="14" customWidth="1"/>
+    <col min="4" max="4" width="67.42578125" style="10" customWidth="1"/>
+    <col min="5" max="5" width="23.5703125" style="10" customWidth="1"/>
+    <col min="6" max="6" width="33.85546875" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="8.85546875" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F1" s="15" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="22"/>
-      <c r="B3" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="D3" s="23" t="s">
+      <c r="F1" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="11"/>
+      <c r="B3" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="F3" s="22" t="s">
+      <c r="E3" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="11" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="20"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="20"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="18"/>
+      <c r="A5" s="20"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="20"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="18"/>
+      <c r="A6" s="20"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="20"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="18"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="18"/>
+      <c r="A7" s="20"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="20"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="18"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="18"/>
+      <c r="A8" s="20"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="20"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="18"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="18"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="20"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="18"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="18"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="20"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="18"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="18"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="20"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="18"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="18"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="20"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="18"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="18"/>
+      <c r="A13" s="20"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="20"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="18"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="18"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="20"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="18"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="18"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="20"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="18"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="18"/>
+      <c r="A16" s="20"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="20"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="18"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="18"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="20"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="18"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="18"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="20"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="18"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="18"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="20"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="18"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="18"/>
+      <c r="A20" s="20"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
